--- a/gift_mapping.xlsx
+++ b/gift_mapping.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="700">
   <si>
     <t>level</t>
   </si>
@@ -485,6 +485,9 @@
     <t>温暖相伴</t>
   </si>
   <si>
+    <t>守护天使</t>
+  </si>
+  <si>
     <t>爱心爆爆</t>
   </si>
   <si>
@@ -2106,6 +2109,24 @@
   </si>
   <si>
     <t>爱心无人机</t>
+  </si>
+  <si>
+    <t>芳心至宝</t>
+  </si>
+  <si>
+    <t>甜心怪兽</t>
+  </si>
+  <si>
+    <t>星中有你</t>
+  </si>
+  <si>
+    <t>歪比巴卜</t>
+  </si>
+  <si>
+    <t>旋梦之恋</t>
+  </si>
+  <si>
+    <t>倾城玫瑰</t>
   </si>
 </sst>
 </file>
@@ -3099,7 +3120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C687"/>
+  <dimension ref="A1:C694"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4903,7 +4924,7 @@
         <v>166</v>
       </c>
       <c r="C164">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="165" spans="1:3">
@@ -4914,7 +4935,7 @@
         <v>167</v>
       </c>
       <c r="C165">
-        <v>233</v>
+        <v>500</v>
       </c>
     </row>
     <row r="166" spans="1:3">
@@ -5123,7 +5144,7 @@
         <v>186</v>
       </c>
       <c r="C184">
-        <v>128</v>
+        <v>233</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -5178,7 +5199,7 @@
         <v>191</v>
       </c>
       <c r="C189">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -5189,7 +5210,7 @@
         <v>192</v>
       </c>
       <c r="C190">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -5376,7 +5397,7 @@
         <v>209</v>
       </c>
       <c r="C207">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -6850,7 +6871,7 @@
         <v>343</v>
       </c>
       <c r="C341">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="342" spans="1:3">
@@ -6960,7 +6981,7 @@
         <v>353</v>
       </c>
       <c r="C351">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="352" spans="1:3">
@@ -6982,7 +7003,7 @@
         <v>355</v>
       </c>
       <c r="C353">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -7130,18 +7151,18 @@
     </row>
     <row r="367" spans="1:3">
       <c r="A367" t="s">
+        <v>3</v>
+      </c>
+      <c r="B367" t="s">
         <v>369</v>
       </c>
-      <c r="B367" t="s">
-        <v>370</v>
-      </c>
       <c r="C367">
-        <v>13140</v>
+        <v>10</v>
       </c>
     </row>
     <row r="368" spans="1:3">
       <c r="A368" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B368" t="s">
         <v>371</v>
@@ -7152,7 +7173,7 @@
     </row>
     <row r="369" spans="1:3">
       <c r="A369" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B369" t="s">
         <v>372</v>
@@ -7163,7 +7184,7 @@
     </row>
     <row r="370" spans="1:3">
       <c r="A370" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B370" t="s">
         <v>373</v>
@@ -7174,7 +7195,7 @@
     </row>
     <row r="371" spans="1:3">
       <c r="A371" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B371" t="s">
         <v>374</v>
@@ -7185,7 +7206,7 @@
     </row>
     <row r="372" spans="1:3">
       <c r="A372" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B372" t="s">
         <v>375</v>
@@ -7196,7 +7217,7 @@
     </row>
     <row r="373" spans="1:3">
       <c r="A373" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B373" t="s">
         <v>376</v>
@@ -7207,7 +7228,7 @@
     </row>
     <row r="374" spans="1:3">
       <c r="A374" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B374" t="s">
         <v>377</v>
@@ -7218,7 +7239,7 @@
     </row>
     <row r="375" spans="1:3">
       <c r="A375" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B375" t="s">
         <v>378</v>
@@ -7229,7 +7250,7 @@
     </row>
     <row r="376" spans="1:3">
       <c r="A376" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B376" t="s">
         <v>379</v>
@@ -7240,7 +7261,7 @@
     </row>
     <row r="377" spans="1:3">
       <c r="A377" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B377" t="s">
         <v>380</v>
@@ -7251,7 +7272,7 @@
     </row>
     <row r="378" spans="1:3">
       <c r="A378" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B378" t="s">
         <v>381</v>
@@ -7262,7 +7283,7 @@
     </row>
     <row r="379" spans="1:3">
       <c r="A379" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B379" t="s">
         <v>382</v>
@@ -7273,7 +7294,7 @@
     </row>
     <row r="380" spans="1:3">
       <c r="A380" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B380" t="s">
         <v>383</v>
@@ -7284,7 +7305,7 @@
     </row>
     <row r="381" spans="1:3">
       <c r="A381" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B381" t="s">
         <v>384</v>
@@ -7295,7 +7316,7 @@
     </row>
     <row r="382" spans="1:3">
       <c r="A382" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B382" t="s">
         <v>385</v>
@@ -7306,7 +7327,7 @@
     </row>
     <row r="383" spans="1:3">
       <c r="A383" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B383" t="s">
         <v>386</v>
@@ -7317,7 +7338,7 @@
     </row>
     <row r="384" spans="1:3">
       <c r="A384" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B384" t="s">
         <v>387</v>
@@ -7328,7 +7349,7 @@
     </row>
     <row r="385" spans="1:3">
       <c r="A385" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B385" t="s">
         <v>388</v>
@@ -7339,7 +7360,7 @@
     </row>
     <row r="386" spans="1:3">
       <c r="A386" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B386" t="s">
         <v>389</v>
@@ -7350,7 +7371,7 @@
     </row>
     <row r="387" spans="1:3">
       <c r="A387" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B387" t="s">
         <v>390</v>
@@ -7361,7 +7382,7 @@
     </row>
     <row r="388" spans="1:3">
       <c r="A388" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B388" t="s">
         <v>391</v>
@@ -7372,7 +7393,7 @@
     </row>
     <row r="389" spans="1:3">
       <c r="A389" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B389" t="s">
         <v>392</v>
@@ -7383,7 +7404,7 @@
     </row>
     <row r="390" spans="1:3">
       <c r="A390" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B390" t="s">
         <v>393</v>
@@ -7394,7 +7415,7 @@
     </row>
     <row r="391" spans="1:3">
       <c r="A391" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B391" t="s">
         <v>394</v>
@@ -7405,7 +7426,7 @@
     </row>
     <row r="392" spans="1:3">
       <c r="A392" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B392" t="s">
         <v>395</v>
@@ -7416,7 +7437,7 @@
     </row>
     <row r="393" spans="1:3">
       <c r="A393" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B393" t="s">
         <v>396</v>
@@ -7427,7 +7448,7 @@
     </row>
     <row r="394" spans="1:3">
       <c r="A394" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B394" t="s">
         <v>397</v>
@@ -7438,7 +7459,7 @@
     </row>
     <row r="395" spans="1:3">
       <c r="A395" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B395" t="s">
         <v>398</v>
@@ -7449,7 +7470,7 @@
     </row>
     <row r="396" spans="1:3">
       <c r="A396" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B396" t="s">
         <v>399</v>
@@ -7460,7 +7481,7 @@
     </row>
     <row r="397" spans="1:3">
       <c r="A397" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B397" t="s">
         <v>400</v>
@@ -7471,18 +7492,18 @@
     </row>
     <row r="398" spans="1:3">
       <c r="A398" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B398" t="s">
         <v>401</v>
       </c>
       <c r="C398">
-        <v>8888</v>
+        <v>13140</v>
       </c>
     </row>
     <row r="399" spans="1:3">
       <c r="A399" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B399" t="s">
         <v>402</v>
@@ -7493,7 +7514,7 @@
     </row>
     <row r="400" spans="1:3">
       <c r="A400" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B400" t="s">
         <v>403</v>
@@ -7504,29 +7525,29 @@
     </row>
     <row r="401" spans="1:3">
       <c r="A401" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B401" t="s">
         <v>404</v>
       </c>
       <c r="C401">
-        <v>6666</v>
+        <v>8888</v>
       </c>
     </row>
     <row r="402" spans="1:3">
       <c r="A402" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B402" t="s">
         <v>405</v>
       </c>
       <c r="C402">
-        <v>5200</v>
+        <v>6666</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="A403" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B403" t="s">
         <v>406</v>
@@ -7537,7 +7558,7 @@
     </row>
     <row r="404" spans="1:3">
       <c r="A404" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B404" t="s">
         <v>407</v>
@@ -7548,7 +7569,7 @@
     </row>
     <row r="405" spans="1:3">
       <c r="A405" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B405" t="s">
         <v>408</v>
@@ -7559,7 +7580,7 @@
     </row>
     <row r="406" spans="1:3">
       <c r="A406" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B406" t="s">
         <v>409</v>
@@ -7570,7 +7591,7 @@
     </row>
     <row r="407" spans="1:3">
       <c r="A407" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B407" t="s">
         <v>410</v>
@@ -7581,7 +7602,7 @@
     </row>
     <row r="408" spans="1:3">
       <c r="A408" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B408" t="s">
         <v>411</v>
@@ -7592,7 +7613,7 @@
     </row>
     <row r="409" spans="1:3">
       <c r="A409" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B409" t="s">
         <v>412</v>
@@ -7603,7 +7624,7 @@
     </row>
     <row r="410" spans="1:3">
       <c r="A410" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B410" t="s">
         <v>413</v>
@@ -7614,7 +7635,7 @@
     </row>
     <row r="411" spans="1:3">
       <c r="A411" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B411" t="s">
         <v>414</v>
@@ -7625,7 +7646,7 @@
     </row>
     <row r="412" spans="1:3">
       <c r="A412" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B412" t="s">
         <v>415</v>
@@ -7636,7 +7657,7 @@
     </row>
     <row r="413" spans="1:3">
       <c r="A413" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B413" t="s">
         <v>416</v>
@@ -7647,7 +7668,7 @@
     </row>
     <row r="414" spans="1:3">
       <c r="A414" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B414" t="s">
         <v>417</v>
@@ -7658,7 +7679,7 @@
     </row>
     <row r="415" spans="1:3">
       <c r="A415" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B415" t="s">
         <v>418</v>
@@ -7669,7 +7690,7 @@
     </row>
     <row r="416" spans="1:3">
       <c r="A416" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B416" t="s">
         <v>419</v>
@@ -7680,18 +7701,18 @@
     </row>
     <row r="417" spans="1:3">
       <c r="A417" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B417" t="s">
         <v>420</v>
       </c>
       <c r="C417">
-        <v>3344</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="418" spans="1:3">
       <c r="A418" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B418" t="s">
         <v>421</v>
@@ -7702,7 +7723,7 @@
     </row>
     <row r="419" spans="1:3">
       <c r="A419" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B419" t="s">
         <v>422</v>
@@ -7713,7 +7734,7 @@
     </row>
     <row r="420" spans="1:3">
       <c r="A420" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B420" t="s">
         <v>423</v>
@@ -7724,7 +7745,7 @@
     </row>
     <row r="421" spans="1:3">
       <c r="A421" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B421" t="s">
         <v>424</v>
@@ -7735,7 +7756,7 @@
     </row>
     <row r="422" spans="1:3">
       <c r="A422" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B422" t="s">
         <v>425</v>
@@ -7746,7 +7767,7 @@
     </row>
     <row r="423" spans="1:3">
       <c r="A423" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B423" t="s">
         <v>426</v>
@@ -7757,7 +7778,7 @@
     </row>
     <row r="424" spans="1:3">
       <c r="A424" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B424" t="s">
         <v>427</v>
@@ -7768,7 +7789,7 @@
     </row>
     <row r="425" spans="1:3">
       <c r="A425" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B425" t="s">
         <v>428</v>
@@ -7779,7 +7800,7 @@
     </row>
     <row r="426" spans="1:3">
       <c r="A426" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B426" t="s">
         <v>429</v>
@@ -7790,7 +7811,7 @@
     </row>
     <row r="427" spans="1:3">
       <c r="A427" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B427" t="s">
         <v>430</v>
@@ -7801,7 +7822,7 @@
     </row>
     <row r="428" spans="1:3">
       <c r="A428" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B428" t="s">
         <v>431</v>
@@ -7812,7 +7833,7 @@
     </row>
     <row r="429" spans="1:3">
       <c r="A429" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B429" t="s">
         <v>432</v>
@@ -7823,7 +7844,7 @@
     </row>
     <row r="430" spans="1:3">
       <c r="A430" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B430" t="s">
         <v>433</v>
@@ -7834,7 +7855,7 @@
     </row>
     <row r="431" spans="1:3">
       <c r="A431" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B431" t="s">
         <v>434</v>
@@ -7845,7 +7866,7 @@
     </row>
     <row r="432" spans="1:3">
       <c r="A432" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B432" t="s">
         <v>435</v>
@@ -7856,7 +7877,7 @@
     </row>
     <row r="433" spans="1:3">
       <c r="A433" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B433" t="s">
         <v>436</v>
@@ -7867,7 +7888,7 @@
     </row>
     <row r="434" spans="1:3">
       <c r="A434" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B434" t="s">
         <v>437</v>
@@ -7878,7 +7899,7 @@
     </row>
     <row r="435" spans="1:3">
       <c r="A435" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B435" t="s">
         <v>438</v>
@@ -7889,7 +7910,7 @@
     </row>
     <row r="436" spans="1:3">
       <c r="A436" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B436" t="s">
         <v>439</v>
@@ -7900,7 +7921,7 @@
     </row>
     <row r="437" spans="1:3">
       <c r="A437" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B437" t="s">
         <v>440</v>
@@ -7911,7 +7932,7 @@
     </row>
     <row r="438" spans="1:3">
       <c r="A438" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B438" t="s">
         <v>441</v>
@@ -7922,7 +7943,7 @@
     </row>
     <row r="439" spans="1:3">
       <c r="A439" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B439" t="s">
         <v>442</v>
@@ -7933,7 +7954,7 @@
     </row>
     <row r="440" spans="1:3">
       <c r="A440" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B440" t="s">
         <v>443</v>
@@ -7944,7 +7965,7 @@
     </row>
     <row r="441" spans="1:3">
       <c r="A441" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B441" t="s">
         <v>444</v>
@@ -7955,7 +7976,7 @@
     </row>
     <row r="442" spans="1:3">
       <c r="A442" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B442" t="s">
         <v>445</v>
@@ -7966,7 +7987,7 @@
     </row>
     <row r="443" spans="1:3">
       <c r="A443" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B443" t="s">
         <v>446</v>
@@ -7977,7 +7998,7 @@
     </row>
     <row r="444" spans="1:3">
       <c r="A444" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B444" t="s">
         <v>447</v>
@@ -7988,7 +8009,7 @@
     </row>
     <row r="445" spans="1:3">
       <c r="A445" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B445" t="s">
         <v>448</v>
@@ -7999,7 +8020,7 @@
     </row>
     <row r="446" spans="1:3">
       <c r="A446" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B446" t="s">
         <v>449</v>
@@ -8010,7 +8031,7 @@
     </row>
     <row r="447" spans="1:3">
       <c r="A447" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B447" t="s">
         <v>450</v>
@@ -8021,7 +8042,7 @@
     </row>
     <row r="448" spans="1:3">
       <c r="A448" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B448" t="s">
         <v>451</v>
@@ -8032,7 +8053,7 @@
     </row>
     <row r="449" spans="1:3">
       <c r="A449" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B449" t="s">
         <v>452</v>
@@ -8043,7 +8064,7 @@
     </row>
     <row r="450" spans="1:3">
       <c r="A450" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B450" t="s">
         <v>453</v>
@@ -8054,7 +8075,7 @@
     </row>
     <row r="451" spans="1:3">
       <c r="A451" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B451" t="s">
         <v>454</v>
@@ -8065,7 +8086,7 @@
     </row>
     <row r="452" spans="1:3">
       <c r="A452" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B452" t="s">
         <v>455</v>
@@ -8076,7 +8097,7 @@
     </row>
     <row r="453" spans="1:3">
       <c r="A453" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B453" t="s">
         <v>456</v>
@@ -8087,7 +8108,7 @@
     </row>
     <row r="454" spans="1:3">
       <c r="A454" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B454" t="s">
         <v>457</v>
@@ -8098,7 +8119,7 @@
     </row>
     <row r="455" spans="1:3">
       <c r="A455" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B455" t="s">
         <v>458</v>
@@ -8109,7 +8130,7 @@
     </row>
     <row r="456" spans="1:3">
       <c r="A456" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B456" t="s">
         <v>459</v>
@@ -8120,7 +8141,7 @@
     </row>
     <row r="457" spans="1:3">
       <c r="A457" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B457" t="s">
         <v>460</v>
@@ -8131,29 +8152,29 @@
     </row>
     <row r="458" spans="1:3">
       <c r="A458" t="s">
+        <v>370</v>
+      </c>
+      <c r="B458" t="s">
         <v>461</v>
       </c>
-      <c r="B458" t="s">
-        <v>462</v>
-      </c>
       <c r="C458">
-        <v>188888</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="A459" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B459" t="s">
         <v>463</v>
       </c>
       <c r="C459">
-        <v>131400</v>
+        <v>188888</v>
       </c>
     </row>
     <row r="460" spans="1:3">
       <c r="A460" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B460" t="s">
         <v>464</v>
@@ -8164,7 +8185,7 @@
     </row>
     <row r="461" spans="1:3">
       <c r="A461" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B461" t="s">
         <v>465</v>
@@ -8175,7 +8196,7 @@
     </row>
     <row r="462" spans="1:3">
       <c r="A462" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B462" t="s">
         <v>466</v>
@@ -8186,7 +8207,7 @@
     </row>
     <row r="463" spans="1:3">
       <c r="A463" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B463" t="s">
         <v>467</v>
@@ -8197,7 +8218,7 @@
     </row>
     <row r="464" spans="1:3">
       <c r="A464" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B464" t="s">
         <v>468</v>
@@ -8208,18 +8229,18 @@
     </row>
     <row r="465" spans="1:3">
       <c r="A465" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B465" t="s">
         <v>469</v>
       </c>
       <c r="C465">
-        <v>99999</v>
+        <v>131400</v>
       </c>
     </row>
     <row r="466" spans="1:3">
       <c r="A466" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B466" t="s">
         <v>470</v>
@@ -8230,7 +8251,7 @@
     </row>
     <row r="467" spans="1:3">
       <c r="A467" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B467" t="s">
         <v>471</v>
@@ -8241,7 +8262,7 @@
     </row>
     <row r="468" spans="1:3">
       <c r="A468" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B468" t="s">
         <v>472</v>
@@ -8252,7 +8273,7 @@
     </row>
     <row r="469" spans="1:3">
       <c r="A469" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B469" t="s">
         <v>473</v>
@@ -8263,18 +8284,18 @@
     </row>
     <row r="470" spans="1:3">
       <c r="A470" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B470" t="s">
         <v>474</v>
       </c>
       <c r="C470">
-        <v>52000</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="471" spans="1:3">
       <c r="A471" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B471" t="s">
         <v>475</v>
@@ -8285,7 +8306,7 @@
     </row>
     <row r="472" spans="1:3">
       <c r="A472" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B472" t="s">
         <v>476</v>
@@ -8296,7 +8317,7 @@
     </row>
     <row r="473" spans="1:3">
       <c r="A473" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B473" t="s">
         <v>477</v>
@@ -8307,7 +8328,7 @@
     </row>
     <row r="474" spans="1:3">
       <c r="A474" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B474" t="s">
         <v>478</v>
@@ -8318,7 +8339,7 @@
     </row>
     <row r="475" spans="1:3">
       <c r="A475" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B475" t="s">
         <v>479</v>
@@ -8329,7 +8350,7 @@
     </row>
     <row r="476" spans="1:3">
       <c r="A476" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B476" t="s">
         <v>480</v>
@@ -8340,7 +8361,7 @@
     </row>
     <row r="477" spans="1:3">
       <c r="A477" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B477" t="s">
         <v>481</v>
@@ -8351,7 +8372,7 @@
     </row>
     <row r="478" spans="1:3">
       <c r="A478" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B478" t="s">
         <v>482</v>
@@ -8362,7 +8383,7 @@
     </row>
     <row r="479" spans="1:3">
       <c r="A479" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B479" t="s">
         <v>483</v>
@@ -8373,7 +8394,7 @@
     </row>
     <row r="480" spans="1:3">
       <c r="A480" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B480" t="s">
         <v>484</v>
@@ -8384,7 +8405,7 @@
     </row>
     <row r="481" spans="1:3">
       <c r="A481" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B481" t="s">
         <v>485</v>
@@ -8395,7 +8416,7 @@
     </row>
     <row r="482" spans="1:3">
       <c r="A482" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B482" t="s">
         <v>486</v>
@@ -8406,7 +8427,7 @@
     </row>
     <row r="483" spans="1:3">
       <c r="A483" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B483" t="s">
         <v>487</v>
@@ -8417,7 +8438,7 @@
     </row>
     <row r="484" spans="1:3">
       <c r="A484" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B484" t="s">
         <v>488</v>
@@ -8428,7 +8449,7 @@
     </row>
     <row r="485" spans="1:3">
       <c r="A485" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B485" t="s">
         <v>489</v>
@@ -8439,7 +8460,7 @@
     </row>
     <row r="486" spans="1:3">
       <c r="A486" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B486" t="s">
         <v>490</v>
@@ -8450,7 +8471,7 @@
     </row>
     <row r="487" spans="1:3">
       <c r="A487" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B487" t="s">
         <v>491</v>
@@ -8461,7 +8482,7 @@
     </row>
     <row r="488" spans="1:3">
       <c r="A488" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B488" t="s">
         <v>492</v>
@@ -8472,7 +8493,7 @@
     </row>
     <row r="489" spans="1:3">
       <c r="A489" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B489" t="s">
         <v>493</v>
@@ -8483,7 +8504,7 @@
     </row>
     <row r="490" spans="1:3">
       <c r="A490" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B490" t="s">
         <v>494</v>
@@ -8494,7 +8515,7 @@
     </row>
     <row r="491" spans="1:3">
       <c r="A491" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B491" t="s">
         <v>495</v>
@@ -8505,7 +8526,7 @@
     </row>
     <row r="492" spans="1:3">
       <c r="A492" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B492" t="s">
         <v>496</v>
@@ -8516,7 +8537,7 @@
     </row>
     <row r="493" spans="1:3">
       <c r="A493" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B493" t="s">
         <v>497</v>
@@ -8527,7 +8548,7 @@
     </row>
     <row r="494" spans="1:3">
       <c r="A494" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B494" t="s">
         <v>498</v>
@@ -8538,7 +8559,7 @@
     </row>
     <row r="495" spans="1:3">
       <c r="A495" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B495" t="s">
         <v>499</v>
@@ -8549,7 +8570,7 @@
     </row>
     <row r="496" spans="1:3">
       <c r="A496" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B496" t="s">
         <v>500</v>
@@ -8560,7 +8581,7 @@
     </row>
     <row r="497" spans="1:3">
       <c r="A497" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B497" t="s">
         <v>501</v>
@@ -8571,7 +8592,7 @@
     </row>
     <row r="498" spans="1:3">
       <c r="A498" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B498" t="s">
         <v>502</v>
@@ -8582,7 +8603,7 @@
     </row>
     <row r="499" spans="1:3">
       <c r="A499" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B499" t="s">
         <v>503</v>
@@ -8593,7 +8614,7 @@
     </row>
     <row r="500" spans="1:3">
       <c r="A500" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B500" t="s">
         <v>504</v>
@@ -8604,7 +8625,7 @@
     </row>
     <row r="501" spans="1:3">
       <c r="A501" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B501" t="s">
         <v>505</v>
@@ -8615,7 +8636,7 @@
     </row>
     <row r="502" spans="1:3">
       <c r="A502" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B502" t="s">
         <v>506</v>
@@ -8626,7 +8647,7 @@
     </row>
     <row r="503" spans="1:3">
       <c r="A503" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B503" t="s">
         <v>507</v>
@@ -8637,7 +8658,7 @@
     </row>
     <row r="504" spans="1:3">
       <c r="A504" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B504" t="s">
         <v>508</v>
@@ -8648,7 +8669,7 @@
     </row>
     <row r="505" spans="1:3">
       <c r="A505" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B505" t="s">
         <v>509</v>
@@ -8659,7 +8680,7 @@
     </row>
     <row r="506" spans="1:3">
       <c r="A506" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B506" t="s">
         <v>510</v>
@@ -8670,7 +8691,7 @@
     </row>
     <row r="507" spans="1:3">
       <c r="A507" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B507" t="s">
         <v>511</v>
@@ -8681,7 +8702,7 @@
     </row>
     <row r="508" spans="1:3">
       <c r="A508" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B508" t="s">
         <v>512</v>
@@ -8692,7 +8713,7 @@
     </row>
     <row r="509" spans="1:3">
       <c r="A509" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B509" t="s">
         <v>513</v>
@@ -8703,7 +8724,7 @@
     </row>
     <row r="510" spans="1:3">
       <c r="A510" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B510" t="s">
         <v>514</v>
@@ -8714,7 +8735,7 @@
     </row>
     <row r="511" spans="1:3">
       <c r="A511" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B511" t="s">
         <v>515</v>
@@ -8725,7 +8746,7 @@
     </row>
     <row r="512" spans="1:3">
       <c r="A512" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B512" t="s">
         <v>516</v>
@@ -8736,7 +8757,7 @@
     </row>
     <row r="513" spans="1:3">
       <c r="A513" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B513" t="s">
         <v>517</v>
@@ -8747,7 +8768,7 @@
     </row>
     <row r="514" spans="1:3">
       <c r="A514" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B514" t="s">
         <v>518</v>
@@ -8758,7 +8779,7 @@
     </row>
     <row r="515" spans="1:3">
       <c r="A515" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B515" t="s">
         <v>519</v>
@@ -8769,7 +8790,7 @@
     </row>
     <row r="516" spans="1:3">
       <c r="A516" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B516" t="s">
         <v>520</v>
@@ -8780,18 +8801,18 @@
     </row>
     <row r="517" spans="1:3">
       <c r="A517" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B517" t="s">
         <v>521</v>
       </c>
       <c r="C517">
-        <v>33440</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="518" spans="1:3">
       <c r="A518" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B518" t="s">
         <v>522</v>
@@ -8802,7 +8823,7 @@
     </row>
     <row r="519" spans="1:3">
       <c r="A519" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B519" t="s">
         <v>523</v>
@@ -8813,7 +8834,7 @@
     </row>
     <row r="520" spans="1:3">
       <c r="A520" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B520" t="s">
         <v>524</v>
@@ -8824,7 +8845,7 @@
     </row>
     <row r="521" spans="1:3">
       <c r="A521" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B521" t="s">
         <v>525</v>
@@ -8835,7 +8856,7 @@
     </row>
     <row r="522" spans="1:3">
       <c r="A522" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B522" t="s">
         <v>526</v>
@@ -8846,7 +8867,7 @@
     </row>
     <row r="523" spans="1:3">
       <c r="A523" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B523" t="s">
         <v>527</v>
@@ -8857,7 +8878,7 @@
     </row>
     <row r="524" spans="1:3">
       <c r="A524" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B524" t="s">
         <v>528</v>
@@ -8868,7 +8889,7 @@
     </row>
     <row r="525" spans="1:3">
       <c r="A525" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B525" t="s">
         <v>529</v>
@@ -8879,7 +8900,7 @@
     </row>
     <row r="526" spans="1:3">
       <c r="A526" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B526" t="s">
         <v>530</v>
@@ -8890,7 +8911,7 @@
     </row>
     <row r="527" spans="1:3">
       <c r="A527" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B527" t="s">
         <v>531</v>
@@ -8901,7 +8922,7 @@
     </row>
     <row r="528" spans="1:3">
       <c r="A528" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B528" t="s">
         <v>532</v>
@@ -8912,7 +8933,7 @@
     </row>
     <row r="529" spans="1:3">
       <c r="A529" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B529" t="s">
         <v>533</v>
@@ -8923,7 +8944,7 @@
     </row>
     <row r="530" spans="1:3">
       <c r="A530" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B530" t="s">
         <v>534</v>
@@ -8934,7 +8955,7 @@
     </row>
     <row r="531" spans="1:3">
       <c r="A531" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B531" t="s">
         <v>535</v>
@@ -8945,7 +8966,7 @@
     </row>
     <row r="532" spans="1:3">
       <c r="A532" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B532" t="s">
         <v>536</v>
@@ -8956,7 +8977,7 @@
     </row>
     <row r="533" spans="1:3">
       <c r="A533" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B533" t="s">
         <v>537</v>
@@ -8967,7 +8988,7 @@
     </row>
     <row r="534" spans="1:3">
       <c r="A534" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B534" t="s">
         <v>538</v>
@@ -8978,7 +8999,7 @@
     </row>
     <row r="535" spans="1:3">
       <c r="A535" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B535" t="s">
         <v>539</v>
@@ -8989,7 +9010,7 @@
     </row>
     <row r="536" spans="1:3">
       <c r="A536" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B536" t="s">
         <v>540</v>
@@ -9000,7 +9021,7 @@
     </row>
     <row r="537" spans="1:3">
       <c r="A537" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B537" t="s">
         <v>541</v>
@@ -9011,7 +9032,7 @@
     </row>
     <row r="538" spans="1:3">
       <c r="A538" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B538" t="s">
         <v>542</v>
@@ -9022,7 +9043,7 @@
     </row>
     <row r="539" spans="1:3">
       <c r="A539" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B539" t="s">
         <v>543</v>
@@ -9033,7 +9054,7 @@
     </row>
     <row r="540" spans="1:3">
       <c r="A540" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B540" t="s">
         <v>544</v>
@@ -9044,7 +9065,7 @@
     </row>
     <row r="541" spans="1:3">
       <c r="A541" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B541" t="s">
         <v>545</v>
@@ -9055,7 +9076,7 @@
     </row>
     <row r="542" spans="1:3">
       <c r="A542" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B542" t="s">
         <v>546</v>
@@ -9066,7 +9087,7 @@
     </row>
     <row r="543" spans="1:3">
       <c r="A543" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B543" t="s">
         <v>547</v>
@@ -9077,7 +9098,7 @@
     </row>
     <row r="544" spans="1:3">
       <c r="A544" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B544" t="s">
         <v>548</v>
@@ -9088,7 +9109,7 @@
     </row>
     <row r="545" spans="1:3">
       <c r="A545" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B545" t="s">
         <v>549</v>
@@ -9099,7 +9120,7 @@
     </row>
     <row r="546" spans="1:3">
       <c r="A546" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B546" t="s">
         <v>550</v>
@@ -9110,7 +9131,7 @@
     </row>
     <row r="547" spans="1:3">
       <c r="A547" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B547" t="s">
         <v>551</v>
@@ -9121,7 +9142,7 @@
     </row>
     <row r="548" spans="1:3">
       <c r="A548" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B548" t="s">
         <v>552</v>
@@ -9132,7 +9153,7 @@
     </row>
     <row r="549" spans="1:3">
       <c r="A549" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B549" t="s">
         <v>553</v>
@@ -9143,7 +9164,7 @@
     </row>
     <row r="550" spans="1:3">
       <c r="A550" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B550" t="s">
         <v>554</v>
@@ -9154,7 +9175,7 @@
     </row>
     <row r="551" spans="1:3">
       <c r="A551" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B551" t="s">
         <v>555</v>
@@ -9165,7 +9186,7 @@
     </row>
     <row r="552" spans="1:3">
       <c r="A552" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B552" t="s">
         <v>556</v>
@@ -9176,7 +9197,7 @@
     </row>
     <row r="553" spans="1:3">
       <c r="A553" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B553" t="s">
         <v>557</v>
@@ -9187,7 +9208,7 @@
     </row>
     <row r="554" spans="1:3">
       <c r="A554" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B554" t="s">
         <v>558</v>
@@ -9198,7 +9219,7 @@
     </row>
     <row r="555" spans="1:3">
       <c r="A555" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B555" t="s">
         <v>559</v>
@@ -9209,7 +9230,7 @@
     </row>
     <row r="556" spans="1:3">
       <c r="A556" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B556" t="s">
         <v>560</v>
@@ -9220,7 +9241,7 @@
     </row>
     <row r="557" spans="1:3">
       <c r="A557" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B557" t="s">
         <v>561</v>
@@ -9231,7 +9252,7 @@
     </row>
     <row r="558" spans="1:3">
       <c r="A558" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B558" t="s">
         <v>562</v>
@@ -9242,7 +9263,7 @@
     </row>
     <row r="559" spans="1:3">
       <c r="A559" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B559" t="s">
         <v>563</v>
@@ -9253,7 +9274,7 @@
     </row>
     <row r="560" spans="1:3">
       <c r="A560" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B560" t="s">
         <v>564</v>
@@ -9264,7 +9285,7 @@
     </row>
     <row r="561" spans="1:3">
       <c r="A561" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B561" t="s">
         <v>565</v>
@@ -9275,7 +9296,7 @@
     </row>
     <row r="562" spans="1:3">
       <c r="A562" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B562" t="s">
         <v>566</v>
@@ -9286,7 +9307,7 @@
     </row>
     <row r="563" spans="1:3">
       <c r="A563" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B563" t="s">
         <v>567</v>
@@ -9297,7 +9318,7 @@
     </row>
     <row r="564" spans="1:3">
       <c r="A564" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B564" t="s">
         <v>568</v>
@@ -9308,7 +9329,7 @@
     </row>
     <row r="565" spans="1:3">
       <c r="A565" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B565" t="s">
         <v>569</v>
@@ -9319,7 +9340,7 @@
     </row>
     <row r="566" spans="1:3">
       <c r="A566" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B566" t="s">
         <v>570</v>
@@ -9330,7 +9351,7 @@
     </row>
     <row r="567" spans="1:3">
       <c r="A567" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B567" t="s">
         <v>571</v>
@@ -9341,7 +9362,7 @@
     </row>
     <row r="568" spans="1:3">
       <c r="A568" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B568" t="s">
         <v>572</v>
@@ -9352,7 +9373,7 @@
     </row>
     <row r="569" spans="1:3">
       <c r="A569" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B569" t="s">
         <v>573</v>
@@ -9363,7 +9384,7 @@
     </row>
     <row r="570" spans="1:3">
       <c r="A570" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B570" t="s">
         <v>574</v>
@@ -9374,7 +9395,7 @@
     </row>
     <row r="571" spans="1:3">
       <c r="A571" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B571" t="s">
         <v>575</v>
@@ -9385,7 +9406,7 @@
     </row>
     <row r="572" spans="1:3">
       <c r="A572" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B572" t="s">
         <v>576</v>
@@ -9396,7 +9417,7 @@
     </row>
     <row r="573" spans="1:3">
       <c r="A573" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B573" t="s">
         <v>577</v>
@@ -9407,7 +9428,7 @@
     </row>
     <row r="574" spans="1:3">
       <c r="A574" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B574" t="s">
         <v>578</v>
@@ -9418,7 +9439,7 @@
     </row>
     <row r="575" spans="1:3">
       <c r="A575" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B575" t="s">
         <v>579</v>
@@ -9429,7 +9450,7 @@
     </row>
     <row r="576" spans="1:3">
       <c r="A576" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B576" t="s">
         <v>580</v>
@@ -9440,7 +9461,7 @@
     </row>
     <row r="577" spans="1:3">
       <c r="A577" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B577" t="s">
         <v>581</v>
@@ -9451,7 +9472,7 @@
     </row>
     <row r="578" spans="1:3">
       <c r="A578" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B578" t="s">
         <v>582</v>
@@ -9462,7 +9483,7 @@
     </row>
     <row r="579" spans="1:3">
       <c r="A579" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B579" t="s">
         <v>583</v>
@@ -9473,7 +9494,7 @@
     </row>
     <row r="580" spans="1:3">
       <c r="A580" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B580" t="s">
         <v>584</v>
@@ -9484,7 +9505,7 @@
     </row>
     <row r="581" spans="1:3">
       <c r="A581" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B581" t="s">
         <v>585</v>
@@ -9495,7 +9516,7 @@
     </row>
     <row r="582" spans="1:3">
       <c r="A582" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B582" t="s">
         <v>586</v>
@@ -9506,7 +9527,7 @@
     </row>
     <row r="583" spans="1:3">
       <c r="A583" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B583" t="s">
         <v>587</v>
@@ -9517,7 +9538,7 @@
     </row>
     <row r="584" spans="1:3">
       <c r="A584" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B584" t="s">
         <v>588</v>
@@ -9528,7 +9549,7 @@
     </row>
     <row r="585" spans="1:3">
       <c r="A585" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B585" t="s">
         <v>589</v>
@@ -9539,7 +9560,7 @@
     </row>
     <row r="586" spans="1:3">
       <c r="A586" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B586" t="s">
         <v>590</v>
@@ -9550,7 +9571,7 @@
     </row>
     <row r="587" spans="1:3">
       <c r="A587" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B587" t="s">
         <v>591</v>
@@ -9561,7 +9582,7 @@
     </row>
     <row r="588" spans="1:3">
       <c r="A588" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B588" t="s">
         <v>592</v>
@@ -9572,7 +9593,7 @@
     </row>
     <row r="589" spans="1:3">
       <c r="A589" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B589" t="s">
         <v>593</v>
@@ -9583,7 +9604,7 @@
     </row>
     <row r="590" spans="1:3">
       <c r="A590" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B590" t="s">
         <v>594</v>
@@ -9594,7 +9615,7 @@
     </row>
     <row r="591" spans="1:3">
       <c r="A591" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B591" t="s">
         <v>595</v>
@@ -9605,7 +9626,7 @@
     </row>
     <row r="592" spans="1:3">
       <c r="A592" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B592" t="s">
         <v>596</v>
@@ -9616,7 +9637,7 @@
     </row>
     <row r="593" spans="1:3">
       <c r="A593" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B593" t="s">
         <v>597</v>
@@ -9627,7 +9648,7 @@
     </row>
     <row r="594" spans="1:3">
       <c r="A594" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B594" t="s">
         <v>598</v>
@@ -9638,7 +9659,7 @@
     </row>
     <row r="595" spans="1:3">
       <c r="A595" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B595" t="s">
         <v>599</v>
@@ -9649,7 +9670,7 @@
     </row>
     <row r="596" spans="1:3">
       <c r="A596" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B596" t="s">
         <v>600</v>
@@ -9660,7 +9681,7 @@
     </row>
     <row r="597" spans="1:3">
       <c r="A597" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B597" t="s">
         <v>601</v>
@@ -9671,7 +9692,7 @@
     </row>
     <row r="598" spans="1:3">
       <c r="A598" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B598" t="s">
         <v>602</v>
@@ -9682,7 +9703,7 @@
     </row>
     <row r="599" spans="1:3">
       <c r="A599" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B599" t="s">
         <v>603</v>
@@ -9693,7 +9714,7 @@
     </row>
     <row r="600" spans="1:3">
       <c r="A600" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B600" t="s">
         <v>604</v>
@@ -9704,7 +9725,7 @@
     </row>
     <row r="601" spans="1:3">
       <c r="A601" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B601" t="s">
         <v>605</v>
@@ -9715,7 +9736,7 @@
     </row>
     <row r="602" spans="1:3">
       <c r="A602" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B602" t="s">
         <v>606</v>
@@ -9726,7 +9747,7 @@
     </row>
     <row r="603" spans="1:3">
       <c r="A603" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B603" t="s">
         <v>607</v>
@@ -9737,7 +9758,7 @@
     </row>
     <row r="604" spans="1:3">
       <c r="A604" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B604" t="s">
         <v>608</v>
@@ -9748,7 +9769,7 @@
     </row>
     <row r="605" spans="1:3">
       <c r="A605" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B605" t="s">
         <v>609</v>
@@ -9759,7 +9780,7 @@
     </row>
     <row r="606" spans="1:3">
       <c r="A606" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B606" t="s">
         <v>610</v>
@@ -9770,7 +9791,7 @@
     </row>
     <row r="607" spans="1:3">
       <c r="A607" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B607" t="s">
         <v>611</v>
@@ -9781,7 +9802,7 @@
     </row>
     <row r="608" spans="1:3">
       <c r="A608" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B608" t="s">
         <v>612</v>
@@ -9792,7 +9813,7 @@
     </row>
     <row r="609" spans="1:3">
       <c r="A609" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B609" t="s">
         <v>613</v>
@@ -9803,7 +9824,7 @@
     </row>
     <row r="610" spans="1:3">
       <c r="A610" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B610" t="s">
         <v>614</v>
@@ -9814,7 +9835,7 @@
     </row>
     <row r="611" spans="1:3">
       <c r="A611" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B611" t="s">
         <v>615</v>
@@ -9825,7 +9846,7 @@
     </row>
     <row r="612" spans="1:3">
       <c r="A612" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B612" t="s">
         <v>616</v>
@@ -9836,7 +9857,7 @@
     </row>
     <row r="613" spans="1:3">
       <c r="A613" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B613" t="s">
         <v>617</v>
@@ -9847,7 +9868,7 @@
     </row>
     <row r="614" spans="1:3">
       <c r="A614" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B614" t="s">
         <v>618</v>
@@ -9858,7 +9879,7 @@
     </row>
     <row r="615" spans="1:3">
       <c r="A615" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B615" t="s">
         <v>619</v>
@@ -9869,7 +9890,7 @@
     </row>
     <row r="616" spans="1:3">
       <c r="A616" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B616" t="s">
         <v>620</v>
@@ -9880,7 +9901,7 @@
     </row>
     <row r="617" spans="1:3">
       <c r="A617" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B617" t="s">
         <v>621</v>
@@ -9891,7 +9912,7 @@
     </row>
     <row r="618" spans="1:3">
       <c r="A618" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B618" t="s">
         <v>622</v>
@@ -9902,7 +9923,7 @@
     </row>
     <row r="619" spans="1:3">
       <c r="A619" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B619" t="s">
         <v>623</v>
@@ -9913,7 +9934,7 @@
     </row>
     <row r="620" spans="1:3">
       <c r="A620" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B620" t="s">
         <v>624</v>
@@ -9924,7 +9945,7 @@
     </row>
     <row r="621" spans="1:3">
       <c r="A621" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B621" t="s">
         <v>625</v>
@@ -9935,7 +9956,7 @@
     </row>
     <row r="622" spans="1:3">
       <c r="A622" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B622" t="s">
         <v>626</v>
@@ -9946,7 +9967,7 @@
     </row>
     <row r="623" spans="1:3">
       <c r="A623" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B623" t="s">
         <v>627</v>
@@ -9957,7 +9978,7 @@
     </row>
     <row r="624" spans="1:3">
       <c r="A624" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B624" t="s">
         <v>628</v>
@@ -9968,7 +9989,7 @@
     </row>
     <row r="625" spans="1:3">
       <c r="A625" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B625" t="s">
         <v>629</v>
@@ -9979,7 +10000,7 @@
     </row>
     <row r="626" spans="1:3">
       <c r="A626" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B626" t="s">
         <v>630</v>
@@ -9990,7 +10011,7 @@
     </row>
     <row r="627" spans="1:3">
       <c r="A627" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B627" t="s">
         <v>631</v>
@@ -10001,7 +10022,7 @@
     </row>
     <row r="628" spans="1:3">
       <c r="A628" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B628" t="s">
         <v>632</v>
@@ -10012,7 +10033,7 @@
     </row>
     <row r="629" spans="1:3">
       <c r="A629" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B629" t="s">
         <v>633</v>
@@ -10023,7 +10044,7 @@
     </row>
     <row r="630" spans="1:3">
       <c r="A630" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B630" t="s">
         <v>634</v>
@@ -10034,7 +10055,7 @@
     </row>
     <row r="631" spans="1:3">
       <c r="A631" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B631" t="s">
         <v>635</v>
@@ -10045,7 +10066,7 @@
     </row>
     <row r="632" spans="1:3">
       <c r="A632" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B632" t="s">
         <v>636</v>
@@ -10056,7 +10077,7 @@
     </row>
     <row r="633" spans="1:3">
       <c r="A633" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B633" t="s">
         <v>637</v>
@@ -10067,7 +10088,7 @@
     </row>
     <row r="634" spans="1:3">
       <c r="A634" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B634" t="s">
         <v>638</v>
@@ -10078,7 +10099,7 @@
     </row>
     <row r="635" spans="1:3">
       <c r="A635" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B635" t="s">
         <v>639</v>
@@ -10089,7 +10110,7 @@
     </row>
     <row r="636" spans="1:3">
       <c r="A636" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B636" t="s">
         <v>640</v>
@@ -10100,7 +10121,7 @@
     </row>
     <row r="637" spans="1:3">
       <c r="A637" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B637" t="s">
         <v>641</v>
@@ -10111,29 +10132,29 @@
     </row>
     <row r="638" spans="1:3">
       <c r="A638" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B638" t="s">
         <v>642</v>
       </c>
       <c r="C638">
-        <v>25000</v>
+        <v>33440</v>
       </c>
     </row>
     <row r="639" spans="1:3">
       <c r="A639" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B639" t="s">
         <v>643</v>
       </c>
       <c r="C639">
-        <v>18888</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="640" spans="1:3">
       <c r="A640" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B640" t="s">
         <v>644</v>
@@ -10144,7 +10165,7 @@
     </row>
     <row r="641" spans="1:3">
       <c r="A641" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B641" t="s">
         <v>645</v>
@@ -10155,7 +10176,7 @@
     </row>
     <row r="642" spans="1:3">
       <c r="A642" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B642" t="s">
         <v>646</v>
@@ -10166,7 +10187,7 @@
     </row>
     <row r="643" spans="1:3">
       <c r="A643" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B643" t="s">
         <v>647</v>
@@ -10177,18 +10198,18 @@
     </row>
     <row r="644" spans="1:3">
       <c r="A644" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B644" t="s">
         <v>648</v>
       </c>
       <c r="C644">
-        <v>18880</v>
+        <v>18888</v>
       </c>
     </row>
     <row r="645" spans="1:3">
       <c r="A645" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B645" t="s">
         <v>649</v>
@@ -10199,13 +10220,13 @@
     </row>
     <row r="646" spans="1:3">
       <c r="A646" t="s">
-        <v>3</v>
+        <v>462</v>
       </c>
       <c r="B646" t="s">
         <v>650</v>
       </c>
       <c r="C646">
-        <v>1999</v>
+        <v>18880</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -10216,7 +10237,7 @@
         <v>651</v>
       </c>
       <c r="C647">
-        <v>1314</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="648" spans="1:3">
@@ -10238,7 +10259,7 @@
         <v>653</v>
       </c>
       <c r="C649">
-        <v>233</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="650" spans="1:3">
@@ -10249,7 +10270,7 @@
         <v>654</v>
       </c>
       <c r="C650">
-        <v>128</v>
+        <v>233</v>
       </c>
     </row>
     <row r="651" spans="1:3">
@@ -10260,7 +10281,7 @@
         <v>655</v>
       </c>
       <c r="C651">
-        <v>99</v>
+        <v>128</v>
       </c>
     </row>
     <row r="652" spans="1:3">
@@ -10271,7 +10292,7 @@
         <v>656</v>
       </c>
       <c r="C652">
-        <v>52</v>
+        <v>99</v>
       </c>
     </row>
     <row r="653" spans="1:3">
@@ -10304,7 +10325,7 @@
         <v>659</v>
       </c>
       <c r="C655">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="656" spans="1:3">
@@ -10315,7 +10336,7 @@
         <v>660</v>
       </c>
       <c r="C656">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="657" spans="1:3">
@@ -10331,18 +10352,18 @@
     </row>
     <row r="658" spans="1:3">
       <c r="A658" t="s">
-        <v>369</v>
+        <v>3</v>
       </c>
       <c r="B658" t="s">
         <v>662</v>
       </c>
       <c r="C658">
-        <v>13140</v>
+        <v>10</v>
       </c>
     </row>
     <row r="659" spans="1:3">
       <c r="A659" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B659" t="s">
         <v>663</v>
@@ -10353,18 +10374,18 @@
     </row>
     <row r="660" spans="1:3">
       <c r="A660" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B660" t="s">
         <v>664</v>
       </c>
       <c r="C660">
-        <v>5200</v>
+        <v>13140</v>
       </c>
     </row>
     <row r="661" spans="1:3">
       <c r="A661" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B661" t="s">
         <v>665</v>
@@ -10375,40 +10396,40 @@
     </row>
     <row r="662" spans="1:3">
       <c r="A662" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B662" t="s">
         <v>666</v>
       </c>
       <c r="C662">
-        <v>3344</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="663" spans="1:3">
       <c r="A663" t="s">
-        <v>461</v>
+        <v>370</v>
       </c>
       <c r="B663" t="s">
         <v>667</v>
       </c>
       <c r="C663">
-        <v>99999</v>
+        <v>3344</v>
       </c>
     </row>
     <row r="664" spans="1:3">
       <c r="A664" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B664" t="s">
         <v>668</v>
       </c>
       <c r="C664">
-        <v>52000</v>
+        <v>99999</v>
       </c>
     </row>
     <row r="665" spans="1:3">
       <c r="A665" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B665" t="s">
         <v>669</v>
@@ -10419,7 +10440,7 @@
     </row>
     <row r="666" spans="1:3">
       <c r="A666" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B666" t="s">
         <v>670</v>
@@ -10430,18 +10451,18 @@
     </row>
     <row r="667" spans="1:3">
       <c r="A667" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B667" t="s">
         <v>671</v>
       </c>
       <c r="C667">
-        <v>33440</v>
+        <v>52000</v>
       </c>
     </row>
     <row r="668" spans="1:3">
       <c r="A668" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B668" t="s">
         <v>672</v>
@@ -10452,7 +10473,7 @@
     </row>
     <row r="669" spans="1:3">
       <c r="A669" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B669" t="s">
         <v>673</v>
@@ -10463,18 +10484,18 @@
     </row>
     <row r="670" spans="1:3">
       <c r="A670" t="s">
+        <v>462</v>
+      </c>
+      <c r="B670" t="s">
         <v>674</v>
       </c>
-      <c r="B670" t="s">
-        <v>675</v>
-      </c>
       <c r="C670">
-        <v>5</v>
+        <v>33440</v>
       </c>
     </row>
     <row r="671" spans="1:3">
       <c r="A671" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B671" t="s">
         <v>676</v>
@@ -10485,13 +10506,13 @@
     </row>
     <row r="672" spans="1:3">
       <c r="A672" t="s">
-        <v>3</v>
+        <v>675</v>
       </c>
       <c r="B672" t="s">
         <v>677</v>
       </c>
       <c r="C672">
-        <v>52</v>
+        <v>5</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -10502,7 +10523,7 @@
         <v>678</v>
       </c>
       <c r="C673">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="674" spans="1:3">
@@ -10513,7 +10534,7 @@
         <v>679</v>
       </c>
       <c r="C674">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="675" spans="1:3">
@@ -10524,7 +10545,7 @@
         <v>680</v>
       </c>
       <c r="C675">
-        <v>128</v>
+        <v>18</v>
       </c>
     </row>
     <row r="676" spans="1:3">
@@ -10535,7 +10556,7 @@
         <v>681</v>
       </c>
       <c r="C676">
-        <v>52</v>
+        <v>128</v>
       </c>
     </row>
     <row r="677" spans="1:3">
@@ -10546,29 +10567,29 @@
         <v>682</v>
       </c>
       <c r="C677">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="678" spans="1:3">
       <c r="A678" t="s">
-        <v>674</v>
+        <v>3</v>
       </c>
       <c r="B678" t="s">
         <v>683</v>
       </c>
       <c r="C678">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="679" spans="1:3">
       <c r="A679" t="s">
-        <v>3</v>
+        <v>675</v>
       </c>
       <c r="B679" t="s">
         <v>684</v>
       </c>
       <c r="C679">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="680" spans="1:3">
@@ -10590,7 +10611,7 @@
         <v>686</v>
       </c>
       <c r="C681">
-        <v>1999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="682" spans="1:3">
@@ -10601,7 +10622,7 @@
         <v>687</v>
       </c>
       <c r="C682">
-        <v>52</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="683" spans="1:3">
@@ -10612,7 +10633,7 @@
         <v>688</v>
       </c>
       <c r="C683">
-        <v>1314</v>
+        <v>52</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -10623,29 +10644,29 @@
         <v>689</v>
       </c>
       <c r="C684">
-        <v>52</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="685" spans="1:3">
       <c r="A685" t="s">
-        <v>461</v>
+        <v>3</v>
       </c>
       <c r="B685" t="s">
         <v>690</v>
       </c>
       <c r="C685">
-        <v>33440</v>
+        <v>52</v>
       </c>
     </row>
     <row r="686" spans="1:3">
       <c r="A686" t="s">
-        <v>3</v>
+        <v>462</v>
       </c>
       <c r="B686" t="s">
         <v>691</v>
       </c>
       <c r="C686">
-        <v>1314</v>
+        <v>33440</v>
       </c>
     </row>
     <row r="687" spans="1:3">
@@ -10656,7 +10677,84 @@
         <v>692</v>
       </c>
       <c r="C687">
-        <v>52</v>
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3">
+      <c r="A688" t="s">
+        <v>3</v>
+      </c>
+      <c r="B688" t="s">
+        <v>693</v>
+      </c>
+      <c r="C688">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3">
+      <c r="A689" t="s">
+        <v>3</v>
+      </c>
+      <c r="B689" t="s">
+        <v>694</v>
+      </c>
+      <c r="C689">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3">
+      <c r="A690" t="s">
+        <v>3</v>
+      </c>
+      <c r="B690" t="s">
+        <v>695</v>
+      </c>
+      <c r="C690">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3">
+      <c r="A691" t="s">
+        <v>3</v>
+      </c>
+      <c r="B691" t="s">
+        <v>696</v>
+      </c>
+      <c r="C691">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3">
+      <c r="A692" t="s">
+        <v>3</v>
+      </c>
+      <c r="B692" t="s">
+        <v>697</v>
+      </c>
+      <c r="C692">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3">
+      <c r="A693" t="s">
+        <v>462</v>
+      </c>
+      <c r="B693" t="s">
+        <v>698</v>
+      </c>
+      <c r="C693">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3">
+      <c r="A694" t="s">
+        <v>462</v>
+      </c>
+      <c r="B694" t="s">
+        <v>699</v>
+      </c>
+      <c r="C694">
+        <v>33440</v>
       </c>
     </row>
   </sheetData>
